--- a/Tendo_Monitoring_data/20260330_New_Tendo_Funnel_scorecard2_0_peso_monthly_dec25.xlsx
+++ b/Tendo_Monitoring_data/20260330_New_Tendo_Funnel_scorecard2_0_peso_monthly_dec25.xlsx
@@ -577,16 +577,16 @@
         <v>13</v>
       </c>
       <c r="D7">
-        <v>1467015.5</v>
+        <v>1625865.5</v>
       </c>
       <c r="E7">
-        <v>569714.981</v>
+        <v>659110.218</v>
       </c>
       <c r="F7">
-        <v>480868.345</v>
+        <v>555510.649</v>
       </c>
       <c r="G7">
-        <v>358738.191</v>
+        <v>433380.495</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -600,16 +600,16 @@
         <v>14</v>
       </c>
       <c r="D8">
-        <v>686888</v>
+        <v>737288</v>
       </c>
       <c r="E8">
-        <v>265273.68</v>
+        <v>311693.402</v>
       </c>
       <c r="F8">
-        <v>255254.93</v>
+        <v>301674.652</v>
       </c>
       <c r="G8">
-        <v>185798.798</v>
+        <v>232218.52</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -761,7 +761,7 @@
         <v>15</v>
       </c>
       <c r="D15">
-        <v>298631</v>
+        <v>337031</v>
       </c>
       <c r="E15">
         <v>132135.672</v>
@@ -850,16 +850,16 @@
         <v>13</v>
       </c>
       <c r="D19">
-        <v>1295599</v>
+        <v>1359998</v>
       </c>
       <c r="E19">
-        <v>496081.098</v>
+        <v>547204.768</v>
       </c>
       <c r="F19">
-        <v>522016.165</v>
+        <v>573139.835</v>
       </c>
       <c r="G19">
-        <v>386742.058</v>
+        <v>437865.728</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -873,16 +873,16 @@
         <v>14</v>
       </c>
       <c r="D20">
-        <v>664371</v>
+        <v>718339</v>
       </c>
       <c r="E20">
-        <v>312593.091</v>
+        <v>325041.619</v>
       </c>
       <c r="F20">
-        <v>284176.774</v>
+        <v>312730.398</v>
       </c>
       <c r="G20">
-        <v>217545.076</v>
+        <v>246098.7</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -988,16 +988,16 @@
         <v>13</v>
       </c>
       <c r="D25">
-        <v>316182</v>
+        <v>563514</v>
       </c>
       <c r="E25">
-        <v>119829.575</v>
+        <v>159370.977</v>
       </c>
       <c r="F25">
-        <v>93914.72900000001</v>
+        <v>142805.958</v>
       </c>
       <c r="G25">
-        <v>88208.49000000001</v>
+        <v>137099.719</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1284,16 +1284,16 @@
         <v>14</v>
       </c>
       <c r="D38">
-        <v>341422</v>
+        <v>353522</v>
       </c>
       <c r="E38">
         <v>168063.446</v>
       </c>
       <c r="F38">
-        <v>188896.263</v>
+        <v>210502.085</v>
       </c>
       <c r="G38">
-        <v>66923.925</v>
+        <v>88529.747</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1330,13 +1330,13 @@
         <v>16</v>
       </c>
       <c r="D40">
-        <v>35208</v>
+        <v>58164</v>
       </c>
       <c r="E40">
-        <v>7985.373</v>
+        <v>13123.491</v>
       </c>
       <c r="F40">
-        <v>7985.373</v>
+        <v>13123.491</v>
       </c>
       <c r="G40">
         <v>1800</v>
